--- a/home_inspection_forms/005_home_visit_safety_checklist--home_inspection_forms.xlsx
+++ b/home_inspection_forms/005_home_visit_safety_checklist--home_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Has a clear path</t>
+          <t>Are there obstacles in the path</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Clear of clutter</t>
+          <t>Are there cluttered conditions</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Are stairs safe</t>
+          <t>Are the stairs safe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Is the home clean</t>
+          <t>Are there areas that are not well-ventilated</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Are exits clear</t>
+          <t>Are there signs of pests or rodents</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Are electrical outlets covered</t>
+          <t>Is the home clean</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Are stairs handrails secure</t>
+          <t>Are electrical outlets covered</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Are smoke alarms installed</t>
+          <t>Are there sharp objects or hazards</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Is the home clean</t>
+          <t>Is the home well-maintained</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Is the home well-ventilated</t>
+          <t>Are there exposed wiring or electrical hazards</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Is the home quiet</t>
+          <t>Are there areas that are well-maintained</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Is the home warm</t>
+          <t>Are there tripping hazards on the stairs</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Date of visit</t>
+          <t>Are there areas that are hot or cold</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Time of visit</t>
+          <t>Are there emergency exit paths or signs</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,20 +870,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Is the home quiet</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Are there exposed sharp objects or edges</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Are there other safety concerns or hazards</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Are there emergency contact numbers on the wall</t>
+          <t>Is the home in good condition</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Is the home well-maintained</t>
+          <t>Is the home safe for visitors</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Is the home well-maintained</t>
+          <t>Home Visit Safety Checklist 21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Are there emergency exit paths</t>
+          <t>Are there any other safety concerns or hazards</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Is the home well-maintained</t>
+          <t>Home Visit Safety Checklist 23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Is the home well-maintained</t>
+          <t>Home Visit Safety Checklist 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1077,13 +1077,128 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Is the home well-maintained</t>
+          <t>Home Visit Safety Checklist 25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Is there a date of visit</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Is there a time of visit</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_28</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Are there any contact numbers on the wall</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_29</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Are there any contact numbers</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1297,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1348,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1365,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1399,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1416,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1450,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1467,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1501,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1518,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1552,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1569,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1603,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1620,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1654,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1671,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1705,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1722,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_11_choices</t>
+          <t>home_visit_safety_checklist_10_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1641,284 +1756,811 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_19_choices</t>
+          <t>home_visit_safety_checklist_11_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_19_choices</t>
+          <t>home_visit_safety_checklist_11_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_19_choices</t>
+          <t>home_visit_safety_checklist_12_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_20_choices</t>
+          <t>home_visit_safety_checklist_12_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_20_choices</t>
+          <t>home_visit_safety_checklist_12_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_20_choices</t>
+          <t>home_visit_safety_checklist_13_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_21_choices</t>
+          <t>home_visit_safety_checklist_13_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_21_choices</t>
+          <t>home_visit_safety_checklist_13_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_21_choices</t>
+          <t>home_visit_safety_checklist_14_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_22_choices</t>
+          <t>home_visit_safety_checklist_14_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_22_choices</t>
+          <t>home_visit_safety_checklist_14_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_22_choices</t>
+          <t>home_visit_safety_checklist_15_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_23_choices</t>
+          <t>home_visit_safety_checklist_15_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_23_choices</t>
+          <t>home_visit_safety_checklist_15_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>home_visit_safety_checklist_24_choices</t>
+          <t>home_visit_safety_checklist_16_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>home_visit_safety_checklist_16_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_16_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_17_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_17_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_17_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_18_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_18_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_18_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_19_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_19_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_19_choices</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_20_choices</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_20_choices</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_20_choices</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_21_choices</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_21_choices</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_21_choices</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_22_choices</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_22_choices</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_22_choices</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_23_choices</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_23_choices</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_23_choices</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>home_visit_safety_checklist_24_choices</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_24_choices</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_24_choices</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_25_choices</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_25_choices</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_25_choices</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_28_choices</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_28_choices</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>home_visit_safety_checklist_28_choices</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
